--- a/KT_Session_Follow_Up_Questions_RESEARCH_WORKING.xlsx
+++ b/KT_Session_Follow_Up_Questions_RESEARCH_WORKING.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lambert/Documents/Projects/SHRSS/00_Temp/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lambert/Documents/Projects/SHRSS/SHRSS_Knowledge_Transfer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DFC09E2-D1A8-8146-88C6-3706D0920FEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5306DB17-CA4D-7A4A-8405-1C85DC233695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1400" yWindow="2660" windowWidth="31780" windowHeight="17140" xr2:uid="{673F71DB-3AF2-7045-A3A5-B0239BB4967C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1401" uniqueCount="393">
   <si>
     <t>Session</t>
   </si>
@@ -1212,6 +1212,9 @@
   </si>
   <si>
     <t>AI-Generated Question?</t>
+  </si>
+  <si>
+    <t>Reasoning</t>
   </si>
 </sst>
 </file>
@@ -1584,7 +1587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D6FDE3-56CA-9048-B54C-5183184814D1}">
-  <dimension ref="A1:J372"/>
+  <dimension ref="A1:K372"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="94.83203125" customWidth="1"/>
@@ -1592,7 +1595,7 @@
     <col min="9" max="9" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1623,8 +1626,11 @@
       <c r="J1" s="1" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="K1" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1638,7 +1644,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1652,7 +1658,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1666,7 +1672,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1680,7 +1686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1694,7 +1700,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1708,7 +1714,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1722,7 +1728,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1736,7 +1742,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1750,7 +1756,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -1764,7 +1770,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -1778,7 +1784,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -1792,7 +1798,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -1806,7 +1812,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -1820,7 +1826,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>8</v>
       </c>
